--- a/光伏配储项目/电价数据/2026/陌山站.xlsx
+++ b/光伏配储项目/电价数据/2026/陌山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3460299999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.84616</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07840000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.32238</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.60388</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17623</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25747</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.12723</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.59309</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6118400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.76401</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21706</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.64658</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68399</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.94924</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53416</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.28084</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40119</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.16015</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.20891</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.39431</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.51752</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.49008</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75442</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.27782</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.1094</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9380499999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8373200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7972100000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5353300000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50154</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43986</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74349</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.92631</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9913500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51218</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53007</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.52073</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48213</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47547</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6874400000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6549400000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.85845</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.51339</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.73284</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53389</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.67602</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.95701</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.79444</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8500700000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.2441</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.68013</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20217</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90335</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2987</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.18615</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.36917</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.1041</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.17076</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6956100000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.05157</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05038</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9266599999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.15396</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94353</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9004</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9381900000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33544</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5221699999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50027</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50404</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45554</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13273</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17248</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.08990999999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.87275</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.70589</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.69241</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.88426</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.87958</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8724400000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.45284</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.86927</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.87183</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.01932</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5499400000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.60663</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8208799999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.69368</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.73288</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.53016</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.84268</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51619</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.59919</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.64576</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.65039</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6630199999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32193</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6297999999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69797</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50958</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.64397</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.7930700000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.78334</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.91271</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6600199999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53546</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8140499999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5841499999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.93492</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.74962</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.62501</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5751499999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71566</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44252</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34294</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5369700000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5155700000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.64112</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46401</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7140299999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6316900000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.54434</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49931</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6686799999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.49361</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.58933</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6935399999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5087200000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65742</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5153799999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50268</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46846</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33248</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02043</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26577</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11935</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.10004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44286</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31363</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.21905</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.17648</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14156</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23741</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16182</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.23954</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20209</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.17893</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.18622</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04237</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009630000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20547</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20214</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.55677</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05962</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05782</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31368</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.34751</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78603</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87022</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6470499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56967</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5542899999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60221</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.90055</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.5876699999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16494</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25732</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32034</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92613</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.53908</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20847</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.20083</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.287</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8600399999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.55427</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19825</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71157</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82721</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6617799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.20311</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.2099</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.27772</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47332</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02112</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26651</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.56637</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.2595</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25414</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.24893</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.14953</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.17715</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.16949</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.13852</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23128</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.17909</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.16558</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.19381</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.16471</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.14383</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.13862</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.19927</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49087</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.27886</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27409</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.56326</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29987</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22859</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.72136</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.52513</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44572</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.59111</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.75186</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44798</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42515</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.57736</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6691</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48052</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49044</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7126399999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.23368</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47813</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22339</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19214</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18206</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17495</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.17658</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17409</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.13423</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22555</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17383</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.20785</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.18547</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.14595</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.13817</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25087</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22252</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.23975</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26115</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21856</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20083</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15071</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22135</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31637</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26545</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27874</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26609</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6449199999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5238400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.18572</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29127</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48579</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63449</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.68298</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8412200000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.51305</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30904</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4989</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.54184</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56716</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6738200000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8470800000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.58327</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7691399999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61086</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6391699999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.29862</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.48492</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21348</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.20884</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23201</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.22116</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.16529</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.15995</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.17722</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.16977</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20376</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17461</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21351</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.14565</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.04762</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.14592</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18316</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.14468</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.04665999999999999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.13629</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14034</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.17927</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.13824</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14069</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.14558</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.04625</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.15539</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16614</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.12951</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.5253300000000001</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.8509800000000001</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26369</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20137</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22672</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.20613</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24066</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.15607</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24545</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.14616</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22479</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.006889999999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.16832</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16558</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.04628</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20495</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.00326</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18578</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16226</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03456</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24159</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009779999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15486</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01435</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04329</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03625</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01228</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03543</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20683</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26117</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26693</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14605</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15011</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14407</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13392</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.04302</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.04267</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.17241</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85482</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8629600000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08652</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.61646</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00203</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06983</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.63412</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7925599999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9882799999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.62113</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84837</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8465900000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8511599999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9552200000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30077</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17037</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24982</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23736</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18725</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18309</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.14351</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.14599</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21525</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25579</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22388</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24296</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.26067</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28358</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28805</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.58489</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.12016</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84554</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.83957</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6861499999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.89361</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57267</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19505</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31046</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53249</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5391699999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.16095</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.85963</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.57125</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7492799999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49078</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.59984</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7236900000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6689299999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.10993</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8679600000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7415499999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6011599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3151</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52766</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48866</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.57763</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31861</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7204199999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43026</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48122</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.47064</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33359</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14754</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04848</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12213</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14601</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18671</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27516</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16114</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20432</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16734</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.55959</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.49024</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36532</v>
       </c>
     </row>
   </sheetData>
